--- a/JsonConverter/ExcelFiles/PerkEffectData.xlsx
+++ b/JsonConverter/ExcelFiles/PerkEffectData.xlsx
@@ -1,50 +1,33 @@
 
-<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
-<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <Application>Microsoft Excel Compatible / Openpyxl 3.1.5</Application>
-  <HeadingPairs>
-    <vt:vector size="2" baseType="variant">
-      <vt:variant>
-        <vt:lpstr>工作表</vt:lpstr>
-      </vt:variant>
-      <vt:variant>
-        <vt:i4>1</vt:i4>
-      </vt:variant>
-    </vt:vector>
-  </HeadingPairs>
-  <TitlesOfParts>
-    <vt:vector size="1" baseType="lpstr">
-      <vt:lpstr>시트1</vt:lpstr>
-    </vt:vector>
-  </TitlesOfParts>
-</Properties>
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
+  <bookViews>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
+  </bookViews>
+  <sheets>
+    <sheet name="시트1" sheetId="1" r:id="rId1"/>
+  </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
+</workbook>
 </file>
 
-<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
-<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <dc:creator>openpyxl</dc:creator>
-  <cp:lastModifiedBy>honey kim</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-07-07T11:39:00Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-08-14T14:29:07Z</dcterms:modified>
-</cp:coreProperties>
-</file>
-
-<file path=docProps\custom.xml><?xml version="1.0" encoding="utf-8"?>
-<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="2" name="ICV">
-    <vt:lpwstr>6F64F0FC0BD147BE9ABE6589EB5E2F7A_12</vt:lpwstr>
-  </property>
-  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="3" name="KSOProductBuildVer">
-    <vt:lpwstr>1033-12.1.0.28032</vt:lpwstr>
-  </property>
-  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="4" name="CalculationRule">
-    <vt:i4>0</vt:i4>
-  </property>
-</Properties>
-</file>
-
-<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="74">
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="79">
   <si>
     <t>이펙트 id</t>
   </si>
@@ -70,15 +53,12 @@
     <t>Id</t>
   </si>
   <si>
-    <t>EffectectType</t>
+    <t>EffectType</t>
   </si>
   <si>
     <t>StatType</t>
   </si>
   <si>
-    <t>EffectType</t>
-  </si>
-  <si>
     <t>ModType</t>
   </si>
   <si>
@@ -190,6 +170,12 @@
     <t>업무 에너지 소모 (합연산)</t>
   </si>
   <si>
+    <t>Effect_EnergyCost_Comp</t>
+  </si>
+  <si>
+    <t>업무 에너지 소모 (곱연산)</t>
+  </si>
+  <si>
     <t>Effect_SlotCount_Flat</t>
   </si>
   <si>
@@ -214,6 +200,12 @@
     <t>에너지 최대치 (합연산)</t>
   </si>
   <si>
+    <t>Effect_EnergyMax_Comp</t>
+  </si>
+  <si>
+    <t>에너지 최대치 (곱연산)</t>
+  </si>
+  <si>
     <t>Effect_EnergyRecover_Flat</t>
   </si>
   <si>
@@ -229,6 +221,12 @@
     <t>에너지 회복량 (합연산)</t>
   </si>
   <si>
+    <t>Effect_EnergyRecover_Comp</t>
+  </si>
+  <si>
+    <t>에너지 회복량 (곱연산)</t>
+  </si>
+  <si>
     <t>Effect_Unlock_Auto05</t>
   </si>
   <si>
@@ -253,7 +251,7 @@
     <t>Effect_Unlock_Gambling01</t>
   </si>
   <si>
-    <t>Work_Gambling_01</t>
+    <t>Work_Manual_03</t>
   </si>
   <si>
     <t>도박 업무 '즉석 복권' 해금</t>
@@ -262,7 +260,7 @@
     <t>Effect_Unlock_Creative01</t>
   </si>
   <si>
-    <t>Work_Creative_01</t>
+    <t>Work_Manual_04</t>
   </si>
   <si>
     <t>창작 업무 '소설 쓰기' 해금</t>
@@ -270,7 +268,7 @@
 </sst>
 </file>
 
-<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
@@ -278,35 +276,18 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Noto Sans KR"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Noto Sans KR"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
@@ -806,156 +787,150 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1017,7 +992,7 @@
 </styleSheet>
 </file>
 
-<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -1299,37 +1274,11 @@
 </a:theme>
 </file>
 
-<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
-  <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
-  </bookViews>
-  <sheets>
-    <sheet name="시트1" sheetId="1" r:id="rId1"/>
-  </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
-</workbook>
-</file>
-
-<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="34.6388888888889" customWidth="1"/>
     <col min="2" max="2" width="12.8055555555556" customWidth="1"/>
@@ -1339,758 +1288,492 @@
     <col min="6" max="6" width="46.8703703703704" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" spans="1:6">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>이펙트 id</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>이펙트 종류</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>적용 스탯</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>보정 방식</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>대상 업무 id</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" spans="1:6">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" spans="1:6">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>Id</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>EffectType</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>StatType</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>ModType</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>TargetId</t>
-        </is>
-      </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" spans="1:6">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Effect_ManualMoney_Add</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>ManualWorkRewardMoney</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Additive</t>
-        </is>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>수동 업무 획득 돈 (합연산)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" spans="1:6">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Effect_ManualMoney_Comp</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>ManualWorkRewardMoney</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Compound</t>
-        </is>
-      </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>수동 업무 획득 돈 (곱연산)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" spans="1:6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Effect_ManualDP_Add</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>ManualWorkRewardDP</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Additive</t>
-        </is>
-      </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>수동 업무 획득 DP (합연산)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" spans="1:6">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Effect_ManualDP_Comp</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>ManualWorkRewardDP</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Compound</t>
-        </is>
-      </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>수동 업무 획득 DP (곱연산)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="18" spans="1:6">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Effect_AutoMoney_Add</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>AutoWorkRewardMoney</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Additive</t>
-        </is>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>자동 업무 획득 돈 (합연산)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="18" spans="1:6">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Effect_AutoMoney_Comp</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>AutoWorkRewardMoney</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Compound</t>
-        </is>
-      </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>자동 업무 획득 돈 (곱연산)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="18" spans="1:6">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Effect_AutoDP_Add</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>AutoWorkRewardDP</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Additive</t>
-        </is>
-      </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>자동 업무 획득 DP (합연산)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="18" spans="1:6">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Effect_AutoDP_Comp</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>AutoWorkRewardDP</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Compound</t>
-        </is>
-      </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>자동 업무 획득 DP (곱연산)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="18" spans="1:6">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Effect_Duration_Add</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>WorkDuration</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Additive</t>
-        </is>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>자동 업무 소요 시간 (합연산)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="18" spans="1:6">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Effect_Duration_Comp</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>WorkDuration</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Compound</t>
-        </is>
-      </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>자동 업무 소요 시간 (곱연산)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" spans="1:6">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Effect_EnergyCost_Flat</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>WorkEnergyCost</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Flat</t>
-        </is>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>업무 에너지 소모 (정수 가감)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" spans="1:6">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Effect_EnergyCost_Add</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>WorkEnergyCost</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Additive</t>
-        </is>
-      </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>업무 에너지 소모 (합연산)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" spans="1:6">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Effect_EnergyCost_Comp</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>WorkEnergyCost</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Compound</t>
-        </is>
-      </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>업무 에너지 소모 (곱연산)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" spans="1:6">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Effect_SlotCount_Flat</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>AutoWorkSlotCount</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Flat</t>
-        </is>
-      </c>
-      <c r="E17" s="2"/>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>자동 업무 슬롯 수 (정수 가감)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="18" spans="1:6">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Effect_EnergyMax_Flat</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>EnergyMax</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Flat</t>
-        </is>
-      </c>
-      <c r="E18" s="2"/>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>에너지 최대치 (정수 가감)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="18" spans="1:6">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Effect_EnergyMax_Add</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>EnergyMax</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Additive</t>
-        </is>
-      </c>
-      <c r="E19" s="2"/>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>에너지 최대치 (합연산)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="18" spans="1:6">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Effect_EnergyMax_Comp</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>EnergyMax</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Compound</t>
-        </is>
-      </c>
-      <c r="E20" s="2"/>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>에너지 최대치 (곱연산)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="18" spans="1:6">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Effect_EnergyRecover_Flat</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>EnergyRecoverRate</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Flat</t>
-        </is>
-      </c>
-      <c r="E21" s="2"/>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>에너지 회복량 (정수 가감)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="18" spans="1:6">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Effect_EnergyRecover_Add</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>EnergyRecoverRate</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Additive</t>
-        </is>
-      </c>
-      <c r="E22" s="2"/>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>에너지 회복량 (합연산)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="18" spans="1:6">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Effect_EnergyRecover_Comp</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>EnergyRecoverRate</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Compound</t>
-        </is>
-      </c>
-      <c r="E23" s="2"/>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>에너지 회복량 (곱연산)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="18" spans="1:6">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Effect_Unlock_Auto05</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Unlock</t>
-        </is>
-      </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Work_Auto_05</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>자동 업무 '해외 영화 번역' 해금</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="18" spans="1:6">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Effect_Unlock_Auto06</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Unlock</t>
-        </is>
-      </c>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Work_Auto_06</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>자동 업무 '게임 기획하기' 해금</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="18" spans="1:6">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Effect_Unlock_Gambling01</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Unlock</t>
-        </is>
-      </c>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Work_Gambling_01</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>도박 업무 '즉석 복권' 해금</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="18" spans="1:6">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Effect_Unlock_Creative01</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Unlock</t>
-        </is>
-      </c>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Work_Creative_01</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>창작 업무 '소설 쓰기' 해금</t>
-        </is>
+    <row r="1" ht="18.15" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="18.15" spans="1:6">
+      <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" ht="18.15" spans="1:6">
+      <c r="A3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" ht="18.15" spans="1:6">
+      <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" ht="18.15" spans="1:6">
+      <c r="A5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" ht="18.15" spans="1:6">
+      <c r="A6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" ht="18.15" spans="1:6">
+      <c r="A7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" ht="18.15" spans="1:6">
+      <c r="A8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" ht="18.15" spans="1:6">
+      <c r="A9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" ht="18.15" spans="1:6">
+      <c r="A10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" ht="18.15" spans="1:6">
+      <c r="A11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" ht="18.15" spans="1:6">
+      <c r="A12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" ht="18.15" spans="1:6">
+      <c r="A13" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" s="1"/>
+      <c r="F13" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" ht="18.15" spans="1:6">
+      <c r="A14" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" ht="18.15" spans="1:6">
+      <c r="A15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="1"/>
+      <c r="F15" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" ht="18.15" spans="1:6">
+      <c r="A16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" ht="18.15" spans="1:6">
+      <c r="A17" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" s="1"/>
+      <c r="F17" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" ht="18.15" spans="1:6">
+      <c r="A18" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" s="1"/>
+      <c r="F18" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" ht="18.15" spans="1:6">
+      <c r="A19" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="1"/>
+      <c r="F19" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" ht="18.15" spans="1:6">
+      <c r="A20" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" s="1"/>
+      <c r="F20" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" ht="18.15" spans="1:6">
+      <c r="A21" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" s="1"/>
+      <c r="F21" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22" ht="18.15" spans="1:6">
+      <c r="A22" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="1"/>
+      <c r="F22" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="23" ht="18.15" spans="1:6">
+      <c r="A23" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" s="1"/>
+      <c r="F23" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" ht="18.15" spans="1:6">
+      <c r="A24" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="25" ht="18.15" spans="1:6">
+      <c r="A25" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26" ht="18.15" spans="1:6">
+      <c r="A26" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="27" ht="18.15" spans="1:6">
+      <c r="A27" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/PerkEffectData.xlsx
+++ b/JsonConverter/ExcelFiles/PerkEffectData.xlsx
@@ -254,7 +254,7 @@
     <t>Work_Manual_03</t>
   </si>
   <si>
-    <t>도박 업무 '즉석 복권' 해금</t>
+    <t>도박 업무 '주사위 굴리기 게임' 해금</t>
   </si>
   <si>
     <t>Effect_Unlock_Creative01</t>
